--- a/per-stock/KEEL/financials.xlsx
+++ b/per-stock/KEEL/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BITF</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bitfarms Ltd</t>
+          <t>Keel Infrastructure Corp.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -498,7 +507,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -515,7 +524,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1199686528</v>
+        <v>3798082304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -545,10 +554,8 @@
           <t>Enterprise value ($)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4031775232</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -580,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-198</v>
+        <v>-96.76922999999999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,10 +601,8 @@
           <t>P/S (TTM)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B10" t="n">
+        <v>17.373226</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -612,7 +617,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-0.20806</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -627,7 +632,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-1.4365801</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -642,7 +647,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-1.71233</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -656,10 +661,8 @@
           <t>ROE</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B14" t="n">
+        <v>-0.54937</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -673,10 +676,8 @@
           <t>Revenue growth (YoY)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B15" t="n">
+        <v>-0.224</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -690,10 +691,8 @@
           <t>Total cash ($)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B16" t="n">
+        <v>357276992</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -707,10 +706,8 @@
           <t>Total debt ($)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B17" t="n">
+        <v>590969984</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -724,14 +721,12 @@
           <t>FCF (TTM, $)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B18" t="n">
+        <v>-407255000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -742,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>602851137</v>
+        <v>603828651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -757,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.98</v>
+        <v>6.29</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -801,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D55</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C55</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B55</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B55:E55)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D53</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C53</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B53</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B53:E53)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1938,13 +2404,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1954,6 +2420,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1964,30 +2431,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -2000,21 +2472,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-736.613966</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-8847300</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-1132093.714638</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-2066233.62591</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-2466870</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>5176290</v>
+        <v>367920</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2023,21 +2496,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2.4e-05</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.048287</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.230478</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2046,21 +2520,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-64958000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-62463000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>10202000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>11969000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>-14462000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>5966000</v>
+        <v>-11354000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2069,21 +2544,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-31325000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-42130000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-23445000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-8965000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>-11747000</v>
-      </c>
       <c r="F5" s="3" t="n">
-        <v>24649000</v>
+        <v>1752000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2092,21 +2568,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-31325000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-42130000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-23445000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-8965000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-11747000</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>24649000</v>
+        <v>1752000</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2115,21 +2592,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-127574000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-139879000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-46258000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-28844000</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>-55553000</v>
-      </c>
       <c r="F7" s="3" t="n">
-        <v>15165000</v>
+        <v>-38373000</v>
       </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2138,21 +2616,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>27694000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>22451000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>33478000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>38337000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>28364000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>24584000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2161,21 +2640,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>63297000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>66496000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>72127000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>83280000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>68063000</v>
-      </c>
       <c r="F9" s="3" t="n">
-        <v>54776000</v>
+        <v>47375000</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2184,21 +2664,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-96283000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-104593000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-13243000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3004000</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>-26209000</v>
-      </c>
       <c r="F10" s="3" t="n">
-        <v>30615000</v>
+        <v>-9602000</v>
       </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2207,21 +2688,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-123977000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-127044000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-46721000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-35333000</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>-54573000</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>6031000</v>
+        <v>-37966000</v>
       </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2230,21 +2712,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-1661000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-2111000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-5242000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-1615000</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>-434000</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>-2536000</v>
+        <v>472000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2253,21 +2736,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>7180000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>1884000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>2150000</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>218000</v>
-      </c>
       <c r="F13" s="3" t="n">
-        <v>573000</v>
+        <v>185000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2276,21 +2760,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>3723000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>4367000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>585000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>460000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>876000</v>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>863000</v>
+        <v>802000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2299,21 +2784,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-96249736.613966</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-106596300</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-23945093.714638</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-21945233.62591</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>-46272870</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>-4307710</v>
+        <v>-39757080</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2322,21 +2808,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-145353000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-65145000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-80769000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-28844000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-55553000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>15165000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2345,21 +2832,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>131583000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>90632000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>89163000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>104703000</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>88123000</v>
-      </c>
       <c r="F17" s="3" t="n">
-        <v>72818000</v>
+        <v>88026000</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2368,21 +2856,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-98388000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-91087000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-28956000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-39626000</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>-51816000</v>
-      </c>
       <c r="F18" s="3" t="n">
-        <v>-16385000</v>
+        <v>-34841000</v>
       </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2390,18 +2879,21 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>602578453</v>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
         <v>556539628</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>555843347</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>500163441</v>
       </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
         <v>448711912</v>
       </c>
     </row>
@@ -2411,18 +2903,21 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>602578453</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>556539628</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>555843347</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>500163441</v>
       </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>448711912</v>
       </c>
     </row>
@@ -2432,18 +2927,21 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
+      <c r="B21" s="3" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
         <v>-0.08</v>
       </c>
     </row>
@@ -2453,18 +2951,21 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="3" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n">
         <v>-0.08</v>
       </c>
     </row>
@@ -2475,21 +2976,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-145353000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-65145000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-80769000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-28844000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-55553000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>15165000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2498,21 +3000,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-145353000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-65145000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-80769000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-28844000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-55553000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>15165000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2521,21 +3024,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-145353000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-65145000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-80769000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-28844000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-55553000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>15165000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2544,21 +3048,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-145353000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-65145000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-80769000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-28844000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-55553000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>15165000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2566,14 +3071,19 @@
           <t>Net Income Discontinuous Operations</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n">
+      <c r="B27" s="3" t="n">
+        <v>-17779000</v>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
         <v>-34511000</v>
       </c>
-      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n">
+      <c r="F27" s="3" t="n">
+        <v>-17180000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
         <v>-12665000</v>
       </c>
     </row>
@@ -2584,21 +3094,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-127574000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-139879000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-46258000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-28844000</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>-55553000</v>
-      </c>
       <c r="F28" s="3" t="n">
-        <v>15165000</v>
+        <v>-38373000</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2607,21 +3118,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>5655000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-2347000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-8639000</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>762000</v>
-      </c>
       <c r="F29" s="3" t="n">
-        <v>-9707000</v>
+        <v>222000</v>
       </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2630,21 +3142,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-127577000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-134224000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-48605000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-37483000</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>-54791000</v>
-      </c>
       <c r="F30" s="3" t="n">
-        <v>5458000</v>
+        <v>-38151000</v>
       </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2653,21 +3166,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-31325000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-91707000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-23445000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-8965000</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>-33835000</v>
-      </c>
       <c r="F31" s="3" t="n">
-        <v>24649000</v>
+        <v>1752000</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2678,11 +3192,12 @@
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
         <v>-22088000</v>
       </c>
-      <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2691,21 +3206,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-25393000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-159000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-9038000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-12723000</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>-8261000</v>
-      </c>
       <c r="F33" s="3" t="n">
-        <v>270000</v>
+        <v>5534000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2714,482 +3230,539 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-1811000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>19181000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>64000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>1897000</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>10563000</v>
-      </c>
       <c r="F34" s="3" t="n">
-        <v>270000</v>
+        <v>5534000</v>
       </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Write Off</t>
+          <t>Other Special Charges</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>19340000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>9102000</v>
-      </c>
+        <v>21596000</v>
+      </c>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n">
-        <v>18824000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>3628000</v>
-      </c>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Impairment Of Capital Assets</t>
+          <t>Write Off</t>
         </is>
       </c>
       <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>19340000</v>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>14620000</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>17230000</v>
-      </c>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
+        <v>9102000</v>
+      </c>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n">
+        <v>18824000</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>3628000</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Security</t>
+          <t>Impairment Of Capital Assets</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-41971000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>-14407000</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>3758000</v>
-      </c>
+        <v>1986000</v>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n">
-        <v>-3486000</v>
+        <v>14620000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>24379000</v>
+        <v>0</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Net Non Operating Interest Income Expense</t>
+          <t>Gain On Sale Of Security</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-2111000</v>
+        <v>-5932000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>-5242000</v>
+        <v>-41971000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>-1615000</v>
+        <v>-14407000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-434000</v>
+        <v>3758000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>-2536000</v>
+        <v>-3782000</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Total Other Finance Cost</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-702000</v>
+        <v>-1661000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3943000</v>
+        <v>-2111000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-75000</v>
+        <v>-5242000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1092000</v>
+        <v>-1615000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2826000</v>
+        <v>472000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Interest Expense Non Operating</t>
+          <t>Total Other Finance Cost</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>7180000</v>
+        <v>1784000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1884000</v>
+        <v>-702000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>2150000</v>
+        <v>3943000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>218000</v>
+        <v>-75000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>573000</v>
+        <v>145000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Interest Income Non Operating</t>
+          <t>Interest Expense Non Operating</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>4367000</v>
+        <v>3600000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>585000</v>
+        <v>7180000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>460000</v>
+        <v>1884000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>876000</v>
+        <v>2150000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>863000</v>
+        <v>185000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Interest Income Non Operating</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-40406000</v>
+        <v>3723000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>-19918000</v>
+        <v>4367000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>-26903000</v>
+        <v>585000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-21503000</v>
+        <v>460000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-16655000</v>
+        <v>802000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>24136000</v>
+        <v>-94591000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>17036000</v>
+        <v>-40406000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>21423000</v>
+        <v>-19918000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>20060000</v>
+        <v>-26903000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>18042000</v>
+        <v>-40375000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Other Taxes</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0</v>
+        <v>68286000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0</v>
+        <v>24136000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>4291000</v>
-      </c>
-      <c r="E44" s="3" t="n"/>
+        <v>17036000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>21423000</v>
+      </c>
       <c r="F44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>40651000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
+          <t>Other Operating Expenses</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>24136000</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>17036000</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>17132000</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>20060000</v>
-      </c>
+        <v>41449000</v>
+      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n">
-        <v>18042000</v>
+        <v>23033000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Selling And Marketing Expense</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>227000</v>
-      </c>
+          <t>Other Taxes</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
       <c r="C46" s="3" t="n">
-        <v>313000</v>
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1092000</v>
+        <v>0</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>118000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>108000</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
+        <v>4291000</v>
+      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>General And Administrative Expense</t>
+          <t>Selling General And Administration</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>23909000</v>
+        <v>26837000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>16723000</v>
+        <v>24136000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>16040000</v>
+        <v>17036000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>19942000</v>
+        <v>17132000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>17934000</v>
+        <v>17618000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Gand A</t>
+          <t>Selling And Marketing Expense</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8384000</v>
+        <v>686000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4373000</v>
+        <v>227000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>877000</v>
+        <v>313000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6344000</v>
+        <v>1092000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5792000</v>
+        <v>115000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Insurance And Claims</t>
+          <t>General And Administrative Expense</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2840000</v>
+        <v>26151000</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2507000</v>
+        <v>23909000</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3441000</v>
+        <v>16723000</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>3160000</v>
+        <v>16040000</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2617000</v>
+        <v>17503000</v>
       </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Salaries And Wages</t>
+          <t>Other Gand A</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>12685000</v>
+        <v>12726000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>9843000</v>
+        <v>8384000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>11722000</v>
+        <v>4373000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>10438000</v>
+        <v>877000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>9525000</v>
+        <v>5845000</v>
       </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Insurance And Claims</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-16270000</v>
+        <v>2026000</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>-2882000</v>
+        <v>2840000</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>-5480000</v>
+        <v>2507000</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-1443000</v>
+        <v>3441000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1387000</v>
+        <v>2135000</v>
       </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Salaries And Wages</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>66496000</v>
+        <v>11399000</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>72127000</v>
+        <v>12685000</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>83280000</v>
+        <v>9843000</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>68063000</v>
+        <v>11722000</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>54776000</v>
+        <v>9523000</v>
       </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>50226000</v>
+        <v>-26305000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>69245000</v>
+        <v>-16270000</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>77800000</v>
+        <v>-2882000</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>66620000</v>
+        <v>-5480000</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>56163000</v>
+        <v>276000</v>
       </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>63297000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>66496000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>72127000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>83280000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>47375000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>36992000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>50226000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>69245000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>77800000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>47651000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B56" s="3" t="n">
+        <v>36992000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>50226000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>69245000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>77800000</v>
       </c>
-      <c r="E54" s="3" t="n">
-        <v>66620000</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>56163000</v>
-      </c>
-      <c r="G54" s="3" t="n"/>
+      <c r="F56" s="3" t="n">
+        <v>47651000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4889,7 +5462,2035 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>602851137</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>601579999</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>563007747</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>557548857</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>553644380</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>602851137</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>601579999</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>563007747</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>557548857</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>553644380</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>220168000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>96007000</v>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>590970000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>683778000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>73684000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>74909000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>25688000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>416110000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>557392000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>608617000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>659037000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>657272000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>996580000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1229844000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>662806000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>714066000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>663869000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>515702000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>678353000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>257658000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>188791000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>141597000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>416110000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>557392000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>608617000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>659037000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>657272000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>13525000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>14309000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>22234000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>23329000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>23253000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>419135000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>560375000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>611356000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>662486000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>661434000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>992338000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1132822000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>662199000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>713485000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>663349000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>419135000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>560375000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>611356000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>662486000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>661434000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>419135000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>560375000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>611356000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>662486000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>661434000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>11477000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>11477000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>11477000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>17043000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5784000</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>22695000</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>3311000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fixed Assets Revaluation Reserve</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>17043000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>5784000</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>22695000</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>3311000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-757834000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-612481000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-459114000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-383992000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-383490000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>110960000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>108284000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>69645000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>70629000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>117296000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1066009000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1064572000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>969438000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>947329000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>927628000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1066009000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1064572000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>969438000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>947329000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>927628000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>647576000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>735969000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>189923000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>165464000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>110269000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>587632000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>587857000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>72871000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>75994000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>27736000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2632000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2761000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1481000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1586000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>5819000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>584935000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>585031000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>69608000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>70921000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>21852000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>11732000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>12584000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>18765000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>19922000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>19937000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>573203000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>572447000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>50843000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>50999000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1915000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>1717000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3422000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>3323000</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2106000</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>2005000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>59944000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>148112000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>117052000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>89470000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>82533000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>2922000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>44477000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>36629000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>20846000</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>128000</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>6035000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>98747000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4076000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>3836000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1793000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1725000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>3469000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>3407000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>3316000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>4242000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>97022000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>607000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>581000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>520000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>4242000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>97022000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>607000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>581000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>520000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>53909000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>46443000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>68499000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>48853000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>57851000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>27189000</v>
+      </c>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>23010000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>10757000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>8153000</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>3736000</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>26720000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>46443000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>68499000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>48853000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>57851000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>8808000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>30172000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>32323000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>13144000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>13793000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n">
+        <v>73000</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>17912000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>16271000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>36176000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>35709000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>43985000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1066711000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1296344000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>801279000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>827950000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>771703000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>491065000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>469879000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>426569000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>549689000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>547573000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>42675000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>57500000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
+        <v>125138000</v>
+      </c>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>9370000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>9549000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>9255000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>16308000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>13381000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1670000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1384000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2634000</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>954000</v>
+      </c>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>5597000</v>
+      </c>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>350000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n">
+        <v>7125000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1760000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>869000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>872000</v>
+      </c>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>869000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>872000</v>
+      </c>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Investmentsin Associatesat Cost</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>869000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>872000</v>
+      </c>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>3025000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>2983000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>2739000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>3449000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>4162000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>2739000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>3449000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>3582000</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>4039000</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>4208000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>433281000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>391727000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>381725000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>501426000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>529680000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-219253000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-189770000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-142575000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-232415000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-187496000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>652534000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>581497000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>524300000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>733841000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>717176000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>14658000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>14538000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>22937000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>64696000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>67161000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>72011000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>20164000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>822000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1627000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>4586000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>378178000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>367241000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>371211000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>528414000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>505885000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>13649000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>115666000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>117922000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>113914000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>114201000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>122169000</v>
+      </c>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>51869000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>63888000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>11408000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>25190000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>25343000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>575646000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>826465000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>374710000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>278261000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>224130000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>170941000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>174726000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>175798000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>70272000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>100967000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>2287000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>3223000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>15705000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>14054000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>28664000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>64739000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5185000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>5474000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>5559000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>17933000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>66922000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>29120000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>6317000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>6121000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>8126000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>9954000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>10410000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>8676000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>6979000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>7112000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>4886000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n">
+        <v>2871000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>6979000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>7112000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>4886000</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>1137000</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>5805000</v>
+      </c>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>16164000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>26774000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>12965000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>32858000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n">
+        <v>1405000</v>
+      </c>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n">
+        <v>15087000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>30178000</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1177000</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>593000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>10807000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>19898000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>9691000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>471000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>5357000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>5471000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>3274000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>3942000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2680000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n"/>
+      <c r="C81" s="3" t="n"/>
+      <c r="D81" s="3" t="n"/>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n">
+        <v>-47000</v>
+      </c>
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>5357000</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>5471000</v>
+      </c>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n">
+        <v>3942000</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2680000</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>1259000</v>
+      </c>
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>357277000</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>573462000</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>86952000</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>85439000</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>38546000</v>
+      </c>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n"/>
+      <c r="C84" s="3" t="n"/>
+      <c r="D84" s="3" t="n">
+        <v>171278000</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>59029000</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>94112000</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>87298000</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>72629000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>357277000</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>573462000</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>86952000</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>85439000</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>38546000</v>
+      </c>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>357277000</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>573462000</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>86952000</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>85439000</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>38546000</v>
+      </c>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6271,13 +8872,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6287,6 +8888,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6297,30 +8899,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -6333,21 +8940,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-126859000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-117924000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-69191000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-93281000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-66659000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-229329000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6355,14 +8963,15 @@
           <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6371,21 +8980,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-113575000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>457000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-843000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1179000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-40000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-321000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6393,22 +9003,23 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
         <v>618858000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>67000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>47544000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6417,21 +9028,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>34704000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>14435000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>23608000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>50142000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6440,21 +9052,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-62172000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-44274000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-9353000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-19016000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-47818000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-74663000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6463,21 +9076,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>398352000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>630962000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>111952000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>110439000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>38546000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>59542000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6486,21 +9100,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>630962000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>111952000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>110439000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>38546000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>59542000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>72913000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6509,21 +9124,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-100000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>55000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>106000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-69000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>22000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6532,21 +9148,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-232651000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>519110000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1458000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>71787000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-20927000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-13393000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6555,21 +9172,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-113126000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>609196000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>15146000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>46368000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>23568000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>50798000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6578,21 +9196,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-113126000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>609196000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>15146000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>46368000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>23568000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>50798000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6601,21 +9220,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>449000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>24265000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>11443000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>263000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6624,21 +9244,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>34706000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>4479000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>23608000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>50142000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6646,14 +9267,15 @@
           <t>Common Stock Payments</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6662,21 +9284,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>34704000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>14435000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>23608000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>50142000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6685,21 +9308,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-113575000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>619315000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-776000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>46365000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-40000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-321000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6708,21 +9332,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-113575000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>619315000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-776000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>46365000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-40000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-321000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6731,21 +9356,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-113575000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>457000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-843000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-1179000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-40000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-321000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6753,22 +9379,23 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
         <v>618858000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>67000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>47544000</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6777,21 +9404,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-54838000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-16436000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>46150000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>99684000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-25654000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>90475000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6800,21 +9428,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-54838000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-16436000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>46150000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>99684000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-25654000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>90475000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6823,13 +9452,18 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>1396000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>167289000</v>
       </c>
-      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="F24" s="3" t="n">
+        <v>28472000</v>
+      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6838,21 +9472,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>4395000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-157665000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>33810000</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>103169000</v>
-      </c>
       <c r="E25" s="3" t="n">
-        <v>36071000</v>
+        <v>131641000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>154476000</v>
+        <v>7599000</v>
       </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6861,21 +9496,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>5362000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-129742000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>107089000</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>155040000</v>
-      </c>
       <c r="E26" s="3" t="n">
-        <v>72666000</v>
+        <v>183512000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>196007000</v>
+        <v>44194000</v>
       </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6884,21 +9520,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-967000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-27923000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-73279000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-51871000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-36595000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-41531000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6907,21 +9544,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>875000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>15500000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>14625000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-16046000</v>
       </c>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6933,18 +9571,19 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>15500000</v>
+        <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>15500000</v>
       </c>
       <c r="E29" s="3" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>32038000</v>
       </c>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6953,21 +9592,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>875000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-875000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-48084000</v>
       </c>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6976,21 +9616,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-60629000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-26935000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>4828000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-18110000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-45679000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-71801000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6999,21 +9640,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>1543000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>17339000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>14181000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>906000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>2139000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>2862000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7022,21 +9664,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-62172000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-44274000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-9353000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-19016000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-47818000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-74663000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7045,21 +9688,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-64687000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-73650000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-59838000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-74265000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-18841000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-154666000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7068,21 +9712,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-64687000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-73650000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-59838000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-74265000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-18841000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-154666000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7090,16 +9735,19 @@
           <t>Taxes Refund Paid</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>7000</v>
+      </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n">
         <v>-159000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-78000</v>
       </c>
-      <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7108,21 +9756,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>2726000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>2960000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>793000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>462000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>411000</v>
       </c>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n">
-        <v>1699000</v>
-      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7131,21 +9780,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-3582000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1268000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-1382000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-499000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-646000</v>
       </c>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n">
-        <v>-365000</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7154,21 +9804,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-9050000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-15931000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>3109000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-14595000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>28528000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-2777000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7176,20 +9827,21 @@
           <t>Change In Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
         <v>487000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-107000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-1178000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>882000</v>
       </c>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7199,22 +9851,23 @@
           <t>Change In Other Current Assets</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
         <v>1625000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>988000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>3767000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>3608000</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="G41" s="3" t="n">
         <v>11465000</v>
       </c>
-      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7222,22 +9875,23 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
         <v>-16344000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>12568000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-11209000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>12531000</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>-25015000</v>
       </c>
-      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7245,22 +9899,23 @@
           <t>Change In Payable</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n">
         <v>-16344000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>12568000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-11209000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>12531000</v>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="G43" s="3" t="n">
         <v>-25015000</v>
       </c>
-      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7268,22 +9923,23 @@
           <t>Change In Account Payable</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
         <v>-15758000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>12134000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-11143000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>12719000</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="G44" s="3" t="n">
         <v>-25091000</v>
       </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7291,22 +9947,23 @@
           <t>Change In Tax Payable</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n">
         <v>-586000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>434000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>-66000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-188000</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="G45" s="3" t="n">
         <v>76000</v>
       </c>
-      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7314,22 +9971,23 @@
           <t>Change In Income Tax Payable</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
         <v>-586000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>434000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-66000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-188000</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="G46" s="3" t="n">
         <v>76000</v>
       </c>
-      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7337,22 +9995,23 @@
           <t>Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n">
         <v>992000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-9580000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-2665000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>11234000</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="G47" s="3" t="n">
         <v>10564000</v>
       </c>
-      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7360,22 +10019,23 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n">
         <v>-1775000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-547000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-2234000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>-429000</v>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="G48" s="3" t="n">
         <v>-4000</v>
       </c>
-      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7383,22 +10043,23 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n">
         <v>-916000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-213000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-1076000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>702000</v>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="G49" s="3" t="n">
         <v>213000</v>
       </c>
-      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7406,22 +10067,23 @@
           <t>Changes In Account Receivables</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n">
         <v>-916000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-213000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>-1076000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>702000</v>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="G50" s="3" t="n">
         <v>213000</v>
       </c>
-      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7430,21 +10092,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>663000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>-5864000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>-65345000</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>-72123000</v>
-      </c>
       <c r="E51" s="3" t="n">
-        <v>-59905000</v>
+        <v>-76599000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-53687000</v>
+        <v>-55429000</v>
       </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7453,21 +10116,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>3664000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>4082000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>2850000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>3784000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>4268000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>4021000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7475,18 +10139,21 @@
           <t>Unrealized Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n"/>
+      <c r="B53" s="3" t="n">
+        <v>41449000</v>
+      </c>
       <c r="C53" s="3" t="n"/>
       <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n">
         <v>23033000</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7495,21 +10162,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>15603000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>26767000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>43226000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>13026000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>18824000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7517,22 +10185,23 @@
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
         <v>5930000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>-2511000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>-3775000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>762000</v>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="G55" s="3" t="n">
         <v>-9970000</v>
       </c>
-      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7540,22 +10209,23 @@
           <t>Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
         <v>5930000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>-2511000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>-3775000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>762000</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="G56" s="3" t="n">
         <v>-9970000</v>
       </c>
-      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7564,21 +10234,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>27694000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>22451000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>33478000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>38337000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>28364000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>24584000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7587,21 +10258,22 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>27694000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>22451000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>33478000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>38337000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>28364000</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>24584000</v>
-      </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7609,22 +10281,23 @@
           <t>Amortization Cash Flow</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
         <v>323000</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>82000</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="F59" s="3" t="n">
         <v>182000</v>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="G59" s="3" t="n">
         <v>169000</v>
       </c>
-      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7632,22 +10305,23 @@
           <t>Amortization Of Intangibles</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n">
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
         <v>323000</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>82000</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>182000</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="G60" s="3" t="n">
         <v>169000</v>
       </c>
-      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7655,22 +10329,23 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n">
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n">
         <v>22128000</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>33396000</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>38213000</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>28182000</v>
       </c>
-      <c r="F61" s="3" t="n">
+      <c r="G61" s="3" t="n">
         <v>24415000</v>
       </c>
-      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7679,21 +10354,22 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
+        <v>1492000</v>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>-24660000</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="D62" s="3" t="n">
         <v>4357000</v>
       </c>
-      <c r="D62" s="3" t="n">
-        <v>-6524000</v>
-      </c>
       <c r="E62" s="3" t="n">
-        <v>-6849000</v>
+        <v>-2810000</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-135913000</v>
+        <v>-10563000</v>
       </c>
       <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7703,16 +10379,17 @@
       </c>
       <c r="B63" s="3" t="n"/>
       <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n">
         <v>-4946000</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="F63" s="3" t="n">
         <v>-1263000</v>
       </c>
-      <c r="F63" s="3" t="n">
+      <c r="G63" s="3" t="n">
         <v>-135902000</v>
       </c>
-      <c r="G63" s="3" t="n">
+      <c r="H63" s="3" t="n">
         <v>104858000</v>
       </c>
     </row>
@@ -7726,10 +10403,11 @@
       <c r="C64" s="3" t="n"/>
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n">
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n">
         <v>259000</v>
       </c>
-      <c r="G64" s="3" t="n">
+      <c r="H64" s="3" t="n">
         <v>218000</v>
       </c>
     </row>
@@ -7739,22 +10417,23 @@
           <t>Gain Loss On Sale Of PPE</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n">
+      <c r="B65" s="3" t="n">
+        <v>-318000</v>
+      </c>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
         <v>-1533000</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="E65" s="3" t="n">
         <v>-1897000</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="F65" s="3" t="n">
         <v>-5586000</v>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="G65" s="3" t="n">
         <v>-270000</v>
       </c>
-      <c r="G65" s="3" t="n">
-        <v>875000</v>
-      </c>
+      <c r="H65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7763,34 +10442,35 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
+        <v>-145353000</v>
+      </c>
+      <c r="C66" s="3" t="n">
         <v>-141175000</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="D66" s="3" t="n">
         <v>-78650000</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="E66" s="3" t="n">
         <v>-9166000</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="F66" s="3" t="n">
         <v>-55553000</v>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>15165000</v>
-      </c>
       <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7812,94 +10492,10 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enterprise value ($)</t>
+          <t>Trailing P/E</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
-        <is>
-          <t>missing from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Trailing P/E</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>missing from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P/S (TTM)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>missing from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ROE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>missing from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Revenue growth (YoY)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>missing from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total cash ($)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>missing from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total debt ($)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>missing from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FCF (TTM, $)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
         <is>
           <t>missing from yfinance</t>
         </is>
